--- a/testdata/DirectGrnDetailsHK2.xlsx
+++ b/testdata/DirectGrnDetailsHK2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915" firstSheet="11" activeTab="15"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6915"/>
   </bookViews>
   <sheets>
     <sheet name="DirectGrnGenUD" sheetId="38" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6230" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5932" uniqueCount="251">
   <si>
     <t>Scenario  : Local Purchase - Stock UOM and Purchase UOM (Similar)</t>
   </si>
@@ -716,9 +716,6 @@
     <t>1810.39779</t>
   </si>
   <si>
-    <t>ROAU-RM-KDK-02</t>
-  </si>
-  <si>
     <t>1106</t>
   </si>
   <si>
@@ -740,9 +737,6 @@
     <t>328.02245</t>
   </si>
   <si>
-    <t>185.06929</t>
-  </si>
-  <si>
     <t>1354</t>
   </si>
   <si>
@@ -761,18 +755,6 @@
     <t>2399.55</t>
   </si>
   <si>
-    <t>4276</t>
-  </si>
-  <si>
-    <t>1383.48923</t>
-  </si>
-  <si>
-    <t>4282</t>
-  </si>
-  <si>
-    <t>1382.93517</t>
-  </si>
-  <si>
     <t>9599</t>
   </si>
   <si>
@@ -783,9 +765,6 @@
   </si>
   <si>
     <t>187.24408</t>
-  </si>
-  <si>
-    <t>270.802</t>
   </si>
   <si>
     <t>272.136</t>
@@ -812,442 +791,13 @@
     <t>564.54791</t>
   </si>
   <si>
-    <t>272.803</t>
-  </si>
-  <si>
     <t>273.47</t>
-  </si>
-  <si>
-    <t>4956</t>
-  </si>
-  <si>
-    <t>1259.93887</t>
-  </si>
-  <si>
-    <t>4958</t>
-  </si>
-  <si>
-    <t>1259.54451</t>
-  </si>
-  <si>
-    <t>4960</t>
-  </si>
-  <si>
-    <t>1259.15047</t>
-  </si>
-  <si>
-    <t>4962</t>
-  </si>
-  <si>
-    <t>1258.75675</t>
-  </si>
-  <si>
-    <t>5204</t>
-  </si>
-  <si>
-    <t>1245.78715</t>
-  </si>
-  <si>
-    <t>5206</t>
-  </si>
-  <si>
-    <t>1245.41702</t>
-  </si>
-  <si>
-    <t>5208</t>
-  </si>
-  <si>
-    <t>1245.04717</t>
-  </si>
-  <si>
-    <t>5210</t>
-  </si>
-  <si>
-    <t>1244.6776</t>
-  </si>
-  <si>
-    <t>5212</t>
-  </si>
-  <si>
-    <t>1244.30832</t>
-  </si>
-  <si>
-    <t>5214</t>
-  </si>
-  <si>
-    <t>1243.93932</t>
-  </si>
-  <si>
-    <t>5216</t>
-  </si>
-  <si>
-    <t>1243.5706</t>
-  </si>
-  <si>
-    <t>5218</t>
-  </si>
-  <si>
-    <t>1243.20217</t>
-  </si>
-  <si>
-    <t>5220</t>
-  </si>
-  <si>
-    <t>1242.83402</t>
-  </si>
-  <si>
-    <t>5222</t>
-  </si>
-  <si>
-    <t>1242.46615</t>
-  </si>
-  <si>
-    <t>5224</t>
-  </si>
-  <si>
-    <t>1242.09856</t>
-  </si>
-  <si>
-    <t>5226</t>
-  </si>
-  <si>
-    <t>1241.73125</t>
-  </si>
-  <si>
-    <t>5228</t>
-  </si>
-  <si>
-    <t>1241.36423</t>
   </si>
   <si>
     <t>5230</t>
   </si>
   <si>
     <t>1240.99749</t>
-  </si>
-  <si>
-    <t>5268</t>
-  </si>
-  <si>
-    <t>1234.88608</t>
-  </si>
-  <si>
-    <t>5274</t>
-  </si>
-  <si>
-    <t>1233.8024</t>
-  </si>
-  <si>
-    <t>5278</t>
-  </si>
-  <si>
-    <t>1233.08131</t>
-  </si>
-  <si>
-    <t>5282</t>
-  </si>
-  <si>
-    <t>1232.36132</t>
-  </si>
-  <si>
-    <t>5284</t>
-  </si>
-  <si>
-    <t>1232.00173</t>
-  </si>
-  <si>
-    <t>5292</t>
-  </si>
-  <si>
-    <t>1230.5661</t>
-  </si>
-  <si>
-    <t>5296</t>
-  </si>
-  <si>
-    <t>1229.84991</t>
-  </si>
-  <si>
-    <t>5298</t>
-  </si>
-  <si>
-    <t>1229.49222</t>
-  </si>
-  <si>
-    <t>5300</t>
-  </si>
-  <si>
-    <t>1229.1348</t>
-  </si>
-  <si>
-    <t>5304</t>
-  </si>
-  <si>
-    <t>1229.21912</t>
-  </si>
-  <si>
-    <t>5308</t>
-  </si>
-  <si>
-    <t>1229.30331</t>
-  </si>
-  <si>
-    <t>5312</t>
-  </si>
-  <si>
-    <t>1229.38737</t>
-  </si>
-  <si>
-    <t>5316</t>
-  </si>
-  <si>
-    <t>1229.47131</t>
-  </si>
-  <si>
-    <t>5322</t>
-  </si>
-  <si>
-    <t>1229.9948</t>
-  </si>
-  <si>
-    <t>5326</t>
-  </si>
-  <si>
-    <t>1230.07812</t>
-  </si>
-  <si>
-    <t>5330</t>
-  </si>
-  <si>
-    <t>1230.16132</t>
-  </si>
-  <si>
-    <t>5334</t>
-  </si>
-  <si>
-    <t>1230.24439</t>
-  </si>
-  <si>
-    <t>5340</t>
-  </si>
-  <si>
-    <t>1230.76525</t>
-  </si>
-  <si>
-    <t>5344</t>
-  </si>
-  <si>
-    <t>1230.84771</t>
-  </si>
-  <si>
-    <t>5348</t>
-  </si>
-  <si>
-    <t>1230.93005</t>
-  </si>
-  <si>
-    <t>5352</t>
-  </si>
-  <si>
-    <t>1231.01227</t>
-  </si>
-  <si>
-    <t>5360</t>
-  </si>
-  <si>
-    <t>1231.96635</t>
-  </si>
-  <si>
-    <t>5362</t>
-  </si>
-  <si>
-    <t>1231.61214</t>
-  </si>
-  <si>
-    <t>5366</t>
-  </si>
-  <si>
-    <t>1231.69363</t>
-  </si>
-  <si>
-    <t>5370</t>
-  </si>
-  <si>
-    <t>1231.77501</t>
-  </si>
-  <si>
-    <t>5376</t>
-  </si>
-  <si>
-    <t>1232.29067</t>
-  </si>
-  <si>
-    <t>5380</t>
-  </si>
-  <si>
-    <t>1232.37145</t>
-  </si>
-  <si>
-    <t>5386</t>
-  </si>
-  <si>
-    <t>1232.88549</t>
-  </si>
-  <si>
-    <t>6742</t>
-  </si>
-  <si>
-    <t>1154.44195</t>
-  </si>
-  <si>
-    <t>6744</t>
-  </si>
-  <si>
-    <t>1154.18332</t>
-  </si>
-  <si>
-    <t>6746</t>
-  </si>
-  <si>
-    <t>1153.92484</t>
-  </si>
-  <si>
-    <t>6748</t>
-  </si>
-  <si>
-    <t>1153.66651</t>
-  </si>
-  <si>
-    <t>6750</t>
-  </si>
-  <si>
-    <t>1153.40834</t>
-  </si>
-  <si>
-    <t>6752</t>
-  </si>
-  <si>
-    <t>1153.15032</t>
-  </si>
-  <si>
-    <t>6754</t>
-  </si>
-  <si>
-    <t>1152.89245</t>
-  </si>
-  <si>
-    <t>6756</t>
-  </si>
-  <si>
-    <t>1152.63473</t>
-  </si>
-  <si>
-    <t>6760</t>
-  </si>
-  <si>
-    <t>1152.11976</t>
-  </si>
-  <si>
-    <t>6764</t>
-  </si>
-  <si>
-    <t>1151.60539</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>268.98049</t>
-  </si>
-  <si>
-    <t>6766</t>
-  </si>
-  <si>
-    <t>1151.34844</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>269.1101</t>
-  </si>
-  <si>
-    <t>6768</t>
-  </si>
-  <si>
-    <t>1151.09164</t>
-  </si>
-  <si>
-    <t>208</t>
-  </si>
-  <si>
-    <t>269.23721</t>
-  </si>
-  <si>
-    <t>6770</t>
-  </si>
-  <si>
-    <t>1150.83499</t>
-  </si>
-  <si>
-    <t>6772</t>
-  </si>
-  <si>
-    <t>1150.57849</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>269.3619</t>
-  </si>
-  <si>
-    <t>212</t>
-  </si>
-  <si>
-    <t>269.48424</t>
-  </si>
-  <si>
-    <t>6774</t>
-  </si>
-  <si>
-    <t>1150.32214</t>
-  </si>
-  <si>
-    <t>6776</t>
-  </si>
-  <si>
-    <t>1150.06594</t>
-  </si>
-  <si>
-    <t>214</t>
-  </si>
-  <si>
-    <t>269.60429</t>
-  </si>
-  <si>
-    <t>216</t>
-  </si>
-  <si>
-    <t>269.72212</t>
-  </si>
-  <si>
-    <t>6778</t>
-  </si>
-  <si>
-    <t>1149.8099</t>
-  </si>
-  <si>
-    <t>6780</t>
-  </si>
-  <si>
-    <t>1149.55401</t>
-  </si>
-  <si>
-    <t>218</t>
-  </si>
-  <si>
-    <t>269.83779</t>
   </si>
   <si>
     <t>220</t>
@@ -1260,6 +810,12 @@
   </si>
   <si>
     <t>1148.22025</t>
+  </si>
+  <si>
+    <t>ROAU-RM-KDK-100</t>
+  </si>
+  <si>
+    <t>ROAU-RM-KDK-101</t>
   </si>
 </sst>
 </file>
@@ -3852,10 +3408,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -4015,7 +3571,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="99">
-        <v>188</v>
+        <v>149</v>
       </c>
       <c r="AW23" s="112">
         <f>AM23</f>
@@ -4054,10 +3610,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="99">
-        <v>398</v>
+        <v>149</v>
       </c>
       <c r="BN23" t="s" s="99">
-        <v>397</v>
+        <v>158</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -25099,10 +24655,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -25301,10 +24857,10 @@
         <v>148</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BN23" s="99" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -25324,10 +24880,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="107" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C24" s="107" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="D24" s="157" t="s">
         <v>12</v>
@@ -25692,6 +25248,7 @@
     <mergeCell ref="A21:B21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -31260,10 +30817,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -35079,10 +34636,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -38898,10 +38455,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -44590,7 +44147,7 @@
         <v>108</v>
       </c>
       <c r="AV23" t="s" s="0">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AW23" s="16">
         <f>AM23</f>
@@ -44629,10 +44186,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -46352,10 +45909,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -46551,13 +46108,13 @@
       <c r="BH23" s="113"/>
       <c r="BI23" s="112"/>
       <c r="BL23" s="112" t="s">
+        <v>221</v>
+      </c>
+      <c r="BM23" s="99" t="s">
+        <v>223</v>
+      </c>
+      <c r="BN23" s="99" t="s">
         <v>222</v>
-      </c>
-      <c r="BM23" s="99" t="s">
-        <v>224</v>
-      </c>
-      <c r="BN23" s="99" t="s">
-        <v>223</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -46577,10 +46134,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="107" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C24" s="107" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="D24" s="157" t="s">
         <v>12</v>
@@ -46776,13 +46333,13 @@
       <c r="BH24" s="113"/>
       <c r="BI24" s="112"/>
       <c r="BL24" s="112" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="BM24" s="99" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="BN24" s="99" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="BO24" s="112">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -48694,10 +48251,10 @@
         <v>148</v>
       </c>
       <c r="BM23" t="s" s="0">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -52513,7 +52070,7 @@
         <v>190</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -54431,7 +53988,7 @@
         <v>190</v>
       </c>
       <c r="BN23" t="s" s="0">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="BO23" s="48">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -58055,10 +57612,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -58214,10 +57771,10 @@
       <c r="AT23" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="99">
+      <c r="AU23" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="99">
+      <c r="AV23" s="99" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="112">
@@ -58254,13 +57811,13 @@
       <c r="BH23" s="113"/>
       <c r="BI23" s="112"/>
       <c r="BL23" s="112" t="s">
-        <v>222</v>
-      </c>
-      <c r="BM23" t="s" s="99">
-        <v>396</v>
-      </c>
-      <c r="BN23" t="s" s="99">
-        <v>395</v>
+        <v>221</v>
+      </c>
+      <c r="BM23" s="99" t="s">
+        <v>246</v>
+      </c>
+      <c r="BN23" s="99" t="s">
+        <v>245</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -59980,10 +59537,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -60143,7 +59700,7 @@
         <v>108</v>
       </c>
       <c r="AV23" s="99" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AW23" s="112">
         <f>AM23</f>
@@ -60182,10 +59739,10 @@
         <v>148</v>
       </c>
       <c r="BM23" s="99" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="BN23" s="99" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
@@ -60205,10 +59762,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="107" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="C24" s="107" t="s">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="D24" s="157" t="s">
         <v>12</v>
@@ -60368,7 +59925,7 @@
         <v>108</v>
       </c>
       <c r="AV24" s="99" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AW24" s="112">
         <f>AM24</f>
@@ -60407,10 +59964,10 @@
         <v>148</v>
       </c>
       <c r="BM24" s="99" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="BN24" s="99" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="BO24" s="112">
         <f>ROUND((((AW24*AZ24)+(BN24*BM24))/(AW24+BN24)),5)</f>
@@ -62130,10 +61687,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="C23" s="107" t="s">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="D23" s="107" t="s">
         <v>12</v>
@@ -62289,10 +61846,10 @@
       <c r="AT23" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="AU23" t="s" s="99">
+      <c r="AU23" s="99" t="s">
         <v>108</v>
       </c>
-      <c r="AV23" t="s" s="99">
+      <c r="AV23" s="99" t="s">
         <v>149</v>
       </c>
       <c r="AW23" s="112">
@@ -62331,11 +61888,11 @@
       <c r="BL23" s="112" t="s">
         <v>148</v>
       </c>
-      <c r="BM23" t="s" s="99">
-        <v>286</v>
-      </c>
-      <c r="BN23" t="s" s="99">
-        <v>285</v>
+      <c r="BM23" s="99" t="s">
+        <v>244</v>
+      </c>
+      <c r="BN23" s="99" t="s">
+        <v>243</v>
       </c>
       <c r="BO23" s="112">
         <f>ROUND((((AW23*AZ23)+(BN23*BM23))/(AW23+BN23)),5)</f>
